--- a/artfynd/A 25564-2024 artfynd.xlsx
+++ b/artfynd/A 25564-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66494953</v>
+        <v>66494943</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590484.6196715723</v>
+        <v>590573</v>
       </c>
       <c r="R2" t="n">
-        <v>7155621.2698358</v>
+        <v>7155480</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,26 +743,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66494945</v>
+        <v>66494942</v>
       </c>
       <c r="B3" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590628.3272674429</v>
+        <v>590573</v>
       </c>
       <c r="R3" t="n">
-        <v>7155475.983330181</v>
+        <v>7155480</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,21 +845,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66494941</v>
+        <v>66494945</v>
       </c>
       <c r="B4" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590572.5267744518</v>
+        <v>590628</v>
       </c>
       <c r="R4" t="n">
-        <v>7155480.357899164</v>
+        <v>7155476</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -987,21 +947,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +963,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66494954</v>
+        <v>66494935</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,38 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590484.6196715723</v>
+        <v>590419</v>
       </c>
       <c r="R5" t="n">
-        <v>7155621.2698358</v>
+        <v>7155615</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,21 +1049,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1134,7 +1065,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66494944</v>
+        <v>66494950</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,38 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590598.4098753354</v>
+        <v>590533</v>
       </c>
       <c r="R6" t="n">
-        <v>7155480.696586575</v>
+        <v>7155565</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1229,21 +1151,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1255,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1273,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66494942</v>
+        <v>66494941</v>
       </c>
       <c r="B7" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590572.5267744518</v>
+        <v>590573</v>
       </c>
       <c r="R7" t="n">
-        <v>7155480.357899164</v>
+        <v>7155480</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1346,21 +1253,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1372,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1390,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66494950</v>
+        <v>66494939</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590533.330204127</v>
+        <v>590475</v>
       </c>
       <c r="R8" t="n">
-        <v>7155564.963426546</v>
+        <v>7155571</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1463,21 +1355,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1489,7 +1371,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1507,50 +1389,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66494938</v>
+        <v>66494937</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590475.3245777396</v>
+        <v>590422</v>
       </c>
       <c r="R9" t="n">
-        <v>7155570.997994632</v>
+        <v>7155585</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1580,26 +1461,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hackspår</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1611,7 +1477,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,50 +1495,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66494936</v>
+        <v>66494944</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590418.7940749446</v>
+        <v>590598</v>
       </c>
       <c r="R10" t="n">
-        <v>7155614.574181333</v>
+        <v>7155481</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1702,26 +1567,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>hackspår</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1733,7 +1583,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1751,19 +1601,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66494949</v>
+        <v>66494946</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1795,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590533.330204127</v>
+        <v>590622</v>
       </c>
       <c r="R11" t="n">
-        <v>7155564.963426546</v>
+        <v>7155529</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1828,21 +1673,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1854,7 +1689,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1872,50 +1707,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66494935</v>
+        <v>66494949</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590418.7940749446</v>
+        <v>590533</v>
       </c>
       <c r="R12" t="n">
-        <v>7155614.574181333</v>
+        <v>7155565</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1945,21 +1779,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1971,7 +1795,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1989,50 +1813,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66494939</v>
+        <v>66494954</v>
       </c>
       <c r="B13" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590475.3245777396</v>
+        <v>590485</v>
       </c>
       <c r="R13" t="n">
-        <v>7155570.997994632</v>
+        <v>7155621</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2062,21 +1885,11 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2088,7 +1901,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2106,15 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66494937</v>
+        <v>66494936</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,38 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590422.2502351792</v>
+        <v>590419</v>
       </c>
       <c r="R14" t="n">
-        <v>7155585.369006478</v>
+        <v>7155615</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2183,19 +1987,14 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,7 +2008,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2227,15 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66494943</v>
+        <v>66494938</v>
       </c>
       <c r="B15" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2267,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590572.5267744518</v>
+        <v>590475</v>
       </c>
       <c r="R15" t="n">
-        <v>7155480.357899164</v>
+        <v>7155571</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2300,19 +2094,14 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,7 +2115,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2344,15 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66494946</v>
+        <v>66494953</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2360,38 +2144,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hundlkippen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590621.5774124011</v>
+        <v>590485</v>
       </c>
       <c r="R16" t="n">
-        <v>7155528.797026965</v>
+        <v>7155621</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2421,19 +2201,14 @@
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2010-09-19</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,7 +2222,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2462,6 +2237,210 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>66494952</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hundlkippen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590500</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7155604</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-09-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-09-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>9526</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>66494951</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hundlkippen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590500</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7155604</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-09-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-09-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>9525</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
